--- a/PRUEBAS A CALIFICAR/Ya procesadas/COLEGIO-LA-GIRALDA-(IED)-501_Ajustado_20260625_104753.xlsx
+++ b/PRUEBAS A CALIFICAR/Ya procesadas/COLEGIO-LA-GIRALDA-(IED)-501_Ajustado_20260625_104753.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Catherine Espinosa\Desktop\PROYECTO JULIANA\PRUEBAS A CALIFICAR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Catherine Espinosa\Desktop\PROYECTO JULIANA\PRUEBAS A CALIFICAR\Ya procesadas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4323CE84-ECBE-4C1F-A2E8-1CACB6BE56F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2AB5C9B-D232-454F-ABE0-7D5E9BB0A9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Resultados" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resultados!$A$1:$AB$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resultados!$A$1:$AB$77</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1991" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="113">
   <si>
     <t>Est.</t>
   </si>
@@ -362,12 +362,6 @@
   </si>
   <si>
     <t>1206221206</t>
-  </si>
-  <si>
-    <t>SHARON LIZETH RAMIREZ CORREDOR</t>
-  </si>
-  <si>
-    <t>1016734719</t>
   </si>
 </sst>
 </file>
@@ -734,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB79"/>
+  <dimension ref="A1:AB77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -7319,100 +7313,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A78" s="2">
-        <v>77</v>
-      </c>
-      <c r="B78" s="3">
-        <v>111001100030</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I78" s="2"/>
-      <c r="J78" s="2"/>
-      <c r="K78" s="2"/>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="2"/>
-      <c r="T78" s="2"/>
-      <c r="U78" s="2"/>
-      <c r="V78" s="2"/>
-      <c r="W78" s="2"/>
-      <c r="X78" s="2"/>
-      <c r="Y78" s="2"/>
-      <c r="Z78" s="2"/>
-      <c r="AA78" s="2"/>
-      <c r="AB78" s="2"/>
-    </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A79" s="2">
-        <v>78</v>
-      </c>
-      <c r="B79" s="3">
-        <v>111001100030</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="2"/>
-      <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" s="2"/>
-      <c r="Q79" s="2"/>
-      <c r="R79" s="2"/>
-      <c r="S79" s="2"/>
-      <c r="T79" s="2"/>
-      <c r="U79" s="2"/>
-      <c r="V79" s="2"/>
-      <c r="W79" s="2"/>
-      <c r="X79" s="2"/>
-      <c r="Y79" s="2"/>
-      <c r="Z79" s="2"/>
-      <c r="AA79" s="2"/>
-      <c r="AB79" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AB1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AB77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>